--- a/projekt 2 rekonstrukcja/porownanie_zbiorow_t.xlsx
+++ b/projekt 2 rekonstrukcja/porownanie_zbiorow_t.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1967,17 +1967,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTEENN</t>
+          <t>DecisionTree\newline+OverSampler\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1989,35 +1989,35 @@
         <v>0.1491</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1876</v>
+        <v>0.1499</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0871</v>
+        <v>0.1216</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0839</v>
+        <v>0.1588</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1876</v>
+        <v>0.1499</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0301</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+OverSampler\newline+UnderSampler</t>
+          <t>AdaBoost\newline+SMOTEENN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2029,19 +2029,19 @@
         <v>0.1491</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1499</v>
+        <v>0.1876</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1216</v>
+        <v>0.0871</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1588</v>
+        <v>0.0839</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1499</v>
+        <v>0.1876</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0259</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="43">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>AdaBoost\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTE\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SMOTE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SVMSMOTE</t>
+          <t>DecisionTree\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE</t>
+          <t>HistGradientBoosting\newline+SMOTE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>HistGradientBoosting\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE\newline+UnderSampler</t>
+          <t>RandomForest\newline+SMOTE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SVMSMOTE</t>
+          <t>RandomForest\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2431,17 +2431,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE</t>
+          <t>AdaBoost\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2459,17 +2459,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>AdaBoost\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2487,17 +2487,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2515,17 +2515,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SVMSMOTE</t>
+          <t>DecisionTree\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2543,17 +2543,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RandomForest\newline+BorderlineSmote\newline+OneSidedSelection</t>
+          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2571,17 +2571,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE</t>
+          <t>HistGradientBoosting\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>RandomForest\newline+BorderlineSmote\newline+OneSidedSelection</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE\newline+UnderSampler</t>
+          <t>RandomForest\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2655,7 +2655,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SVMSMOTE</t>
+          <t>RandomForest\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>AdaBoost\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTE\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SMOTE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4487,12 +4487,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SVMSMOTE</t>
+          <t>DecisionTree\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4515,12 +4515,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE</t>
+          <t>HistGradientBoosting\newline+SMOTE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4543,12 +4543,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>HistGradientBoosting\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4571,12 +4571,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTE\newline+UnderSampler</t>
+          <t>RandomForest\newline+SMOTE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4599,12 +4599,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SVMSMOTE</t>
+          <t>RandomForest\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4627,17 +4627,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE</t>
+          <t>AdaBoost\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4655,17 +4655,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>AdaBoost\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4683,17 +4683,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4711,17 +4711,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SVMSMOTE</t>
+          <t>DecisionTree\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4739,17 +4739,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RandomForest\newline+BorderlineSmote\newline+OneSidedSelection</t>
+          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4767,17 +4767,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE</t>
+          <t>HistGradientBoosting\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>RandomForest\newline+BorderlineSmote\newline+OneSidedSelection</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE\newline+UnderSampler</t>
+          <t>RandomForest\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4851,7 +4851,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SVMSMOTE</t>
+          <t>RandomForest\newline+SMOTE\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5876,7 +5876,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTETomek</t>
+          <t>AdaBoost\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5898,25 +5898,25 @@
         <v>0.587</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5471</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5404</v>
+        <v>0.516</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5804</v>
+        <v>0.5687</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5471</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SVMSMOTE</t>
+          <t>AdaBoost\newline+SMOTETomek</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5938,19 +5938,19 @@
         <v>0.587</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5471</v>
       </c>
       <c r="G28" t="n">
-        <v>0.516</v>
+        <v>0.5404</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5687</v>
+        <v>0.5804</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5471</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0567</v>
+        <v>0.07290000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8556,17 +8556,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SMOTETomek</t>
+          <t>HistGradientBoosting\newline+OverSampler\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8578,35 +8578,35 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5132</v>
+        <v>0.5866</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5178</v>
+        <v>0.5493</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5373</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5132</v>
+        <v>0.5866</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0418</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+OverSampler\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SMOTETomek</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8618,19 +8618,19 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5866</v>
+        <v>0.5132</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5493</v>
+        <v>0.5178</v>
       </c>
       <c r="H95" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5373</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5866</v>
+        <v>0.5132</v>
       </c>
       <c r="J95" t="n">
-        <v>0.068</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="96">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12793,17 +12793,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTETomek</t>
+          <t>RandomForest\newline+OverSampler\newline+OneSidedSelection</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12815,35 +12815,35 @@
         <v>0.828</v>
       </c>
       <c r="F78" t="n">
-        <v>0.791</v>
+        <v>0.7657</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7941</v>
+        <v>0.7682</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8115</v>
+        <v>0.8156</v>
       </c>
       <c r="I78" t="n">
-        <v>0.791</v>
+        <v>0.7657</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0741</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RandomForest\newline+OverSampler\newline+OneSidedSelection</t>
+          <t>HistGradientBoosting\newline+SMOTETomek</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12855,19 +12855,19 @@
         <v>0.828</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7657</v>
+        <v>0.791</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7682</v>
+        <v>0.7941</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8156</v>
+        <v>0.8115</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7657</v>
+        <v>0.791</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1256</v>
+        <v>0.0741</v>
       </c>
     </row>
     <row r="80">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15550,17 +15550,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+SMOTETomek</t>
+          <t>HistGradientBoosting\newline+OverSampler\newline+OneSidedSelection</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15572,35 +15572,35 @@
         <v>0.5413</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5386</v>
+        <v>0.5437</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5687</v>
+        <v>0.5458</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6461</v>
+        <v>0.5871</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5386</v>
+        <v>0.5437</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0564</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+OverSampler\newline+OneSidedSelection</t>
+          <t>AdaBoost\newline+SMOTETomek</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15612,19 +15612,19 @@
         <v>0.5413</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5437</v>
+        <v>0.5386</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5458</v>
+        <v>0.5687</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5871</v>
+        <v>0.6461</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5437</v>
+        <v>0.5386</v>
       </c>
       <c r="J26" t="n">
-        <v>0.059</v>
+        <v>0.0564</v>
       </c>
     </row>
     <row r="27">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20157,7 +20157,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20917,7 +20917,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20987,12 +20987,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+BorderlineSmote\newline+UnderSampler</t>
+          <t>HistGradientBoosting\newline+OverSampler</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -21009,35 +21009,35 @@
         <v>0.7389</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7419</v>
+        <v>0.7389</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7428</v>
+        <v>0.7391</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7463</v>
+        <v>0.7508</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7419</v>
+        <v>0.7389</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0504</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+OverSampler</t>
+          <t>DecisionTree\newline+BorderlineSmote\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21049,19 +21049,19 @@
         <v>0.7389</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7389</v>
+        <v>0.7419</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7391</v>
+        <v>0.7428</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7508</v>
+        <v>0.7463</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7389</v>
+        <v>0.7419</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0309</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="41">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -21427,7 +21427,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+OverSampler\newline+UnderSampler</t>
+          <t>DecisionTree\newline+SVMSMOTE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21449,25 +21449,25 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6917</v>
+        <v>0.6888</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6889</v>
+        <v>0.6868</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6895</v>
+        <v>0.6948</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6917</v>
+        <v>0.6888</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0398</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DecisionTree\newline+SVMSMOTE</t>
+          <t>DecisionTree\newline+OverSampler\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -21489,19 +21489,19 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6888</v>
+        <v>0.6917</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6868</v>
+        <v>0.6889</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6948</v>
+        <v>0.6895</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6888</v>
+        <v>0.6917</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="52">
@@ -21517,7 +21517,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -21557,7 +21557,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21717,7 +21717,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -22027,7 +22027,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RandomForest\newline+BorderlineSmote\newline+UnderSampler</t>
+          <t>RandomForest\newline+SMOTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -22049,25 +22049,25 @@
         <v>0.8074</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8103</v>
+        <v>0.8081</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8088</v>
+        <v>0.8058</v>
       </c>
       <c r="H65" t="n">
         <v>0.8108</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8103</v>
+        <v>0.8081</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0285</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RandomForest\newline+SMOTE</t>
+          <t>RandomForest\newline+BorderlineSmote\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -22089,19 +22089,19 @@
         <v>0.8074</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8081</v>
+        <v>0.8103</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8058</v>
+        <v>0.8088</v>
       </c>
       <c r="H66" t="n">
         <v>0.8108</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8081</v>
+        <v>0.8103</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0251</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="67">
@@ -22157,7 +22157,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -22427,12 +22427,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+BorderlineSmote\newline+UnderSampler</t>
+          <t>RandomForest\newline+OverSampler</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -22449,35 +22449,35 @@
         <v>0.7815</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7836</v>
+        <v>0.784</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7831</v>
+        <v>0.7822</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7881</v>
+        <v>0.787</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7836</v>
+        <v>0.784</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0184</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
+          <t>AdaBoost\newline+BorderlineSmote\newline+UnderSampler</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -22489,35 +22489,35 @@
         <v>0.7815</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7845</v>
+        <v>0.7836</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7842</v>
+        <v>0.7831</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7892</v>
+        <v>0.7881</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7845</v>
+        <v>0.7836</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0358</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RandomForest\newline+OverSampler</t>
+          <t>HistGradientBoosting\newline+SMOTE\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -22529,19 +22529,19 @@
         <v>0.7815</v>
       </c>
       <c r="F77" t="n">
-        <v>0.784</v>
+        <v>0.7845</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7822</v>
+        <v>0.7842</v>
       </c>
       <c r="H77" t="n">
-        <v>0.787</v>
+        <v>0.7892</v>
       </c>
       <c r="I77" t="n">
-        <v>0.784</v>
+        <v>0.7845</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0393</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="78">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -22877,7 +22877,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -22987,12 +22987,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AdaBoost\newline+OverSampler\newline+ClusterCentroids</t>
+          <t>HistGradientBoosting\newline+BorderlineSmote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>HistGradientBoosting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -23009,35 +23009,35 @@
         <v>0.7463</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7487</v>
+        <v>0.7489</v>
       </c>
       <c r="G89" t="n">
-        <v>0.7492</v>
+        <v>0.7471</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7558</v>
+        <v>0.7512</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7487</v>
+        <v>0.7489</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0481</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HistGradientBoosting\newline+BorderlineSmote</t>
+          <t>AdaBoost\newline+OverSampler\newline+ClusterCentroids</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HistGradientBoosting</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -23049,19 +23049,19 @@
         <v>0.7463</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7489</v>
+        <v>0.7487</v>
       </c>
       <c r="G90" t="n">
-        <v>0.7471</v>
+        <v>0.7492</v>
       </c>
       <c r="H90" t="n">
-        <v>0.7512</v>
+        <v>0.7558</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7489</v>
+        <v>0.7487</v>
       </c>
       <c r="J90" t="n">
-        <v>0.039</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="91">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -23277,7 +23277,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -23477,7 +23477,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -23717,7 +23717,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -24077,7 +24077,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -24197,7 +24197,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24954,7 +24954,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -24994,7 +24994,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -25954,7 +25954,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -26274,7 +26274,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -26434,7 +26434,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -26634,7 +26634,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -26714,7 +26714,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -26794,7 +26794,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -28394,7 +28394,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -28794,7 +28794,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -29074,7 +29074,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Over+Under</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -29194,7 +29194,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oversampling</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
